--- a/03_Outputs/Agua_Bosques_Turismo/08_Educacion/educacion.xlsx
+++ b/03_Outputs/Agua_Bosques_Turismo/08_Educacion/educacion.xlsx
@@ -5744,13 +5744,13 @@
         <v>2021</v>
       </c>
       <c r="F164" s="7">
-        <v>0.776179581374824</v>
+        <v>0.901060882607195</v>
       </c>
       <c r="G164" s="9">
-        <v>0.0361085303420689</v>
+        <v>0.0434987143370351</v>
       </c>
       <c r="H164" s="11">
-        <v>0.0180859734942846</v>
+        <v>0.0571936759555273</v>
       </c>
     </row>
     <row r="165">
@@ -5778,13 +5778,13 @@
         <v>2021</v>
       </c>
       <c r="F165" s="7">
-        <v>0.781685452484999</v>
+        <v>0.898374584145499</v>
       </c>
       <c r="G165" s="9">
-        <v>0.0365894431037481</v>
+        <v>0.0457962595026783</v>
       </c>
       <c r="H165" s="11">
-        <v>0.0201105846704061</v>
+        <v>0.061110584216439</v>
       </c>
     </row>
     <row r="166">
@@ -5812,13 +5812,13 @@
         <v>2021</v>
       </c>
       <c r="F166" s="7">
-        <v>0.808399619674067</v>
+        <v>0.924418856993982</v>
       </c>
       <c r="G166" s="9">
-        <v>0.0340611041845194</v>
+        <v>0.0471531226376282</v>
       </c>
       <c r="H166" s="11">
-        <v>0.0537186135094694</v>
+        <v>0.0582136438740334</v>
       </c>
     </row>
     <row r="167">
